--- a/artfynd/A 51953-2025 artfynd.xlsx
+++ b/artfynd/A 51953-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,16 +678,11 @@
         <v>113513124</v>
       </c>
       <c r="B2" t="n">
-        <v>91621</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -789,6 +784,117 @@
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>113513108</v>
+      </c>
+      <c r="B3" t="n">
+        <v>93197</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Iss klack, Dlr</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>517488</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6719061</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2023-07-17</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2023-07-17</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Mäktig drygt 100-årig tallskog</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 51953-2025 artfynd.xlsx
+++ b/artfynd/A 51953-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113513124</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,8 +904,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113513108</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 51953-2025 artfynd.xlsx
+++ b/artfynd/A 51953-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ3"/>
+  <dimension ref="A1:AZ29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -796,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113513108</v>
+        <v>135772351</v>
       </c>
       <c r="B3" t="n">
-        <v>93197</v>
+        <v>93337</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,37 +807,45 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Iss klack, Dlr</t>
+          <t>Lilla Rullputt, Lilla Rullputt, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>517488</v>
+        <v>517448</v>
       </c>
       <c r="R3" t="n">
-        <v>6719061</v>
+        <v>6718981</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -864,12 +872,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-07-17</t>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-07-17</t>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -882,31 +900,3193 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Mäktig drygt 100-årig tallskog</t>
-        </is>
-      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Ulf Lindenbaum</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ulf Lindenbaum</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/135772351</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>113513108</v>
+      </c>
+      <c r="B4" t="n">
+        <v>93197</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Iss klack, Dlr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>517488</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6719061</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2023-07-17</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2023-07-17</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Mäktig drygt 100-årig tallskog</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/113513108</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>135770232</v>
+      </c>
+      <c r="B5" t="n">
+        <v>93345</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Lilla Rullputt, Lilla Rullputt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>517448</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6719043</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>16:27</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>16:27</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135770232</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>135770490</v>
+      </c>
+      <c r="B6" t="n">
+        <v>93345</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Lilla Rullputt, Lilla Rullputt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>517488</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6719027</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>16:37</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>16:37</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135770490</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>135770586</v>
+      </c>
+      <c r="B7" t="n">
+        <v>93345</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Lilla Rullputt, Lilla Rullputt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>517524</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6719005</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>16:41</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>16:41</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135770586</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>135770641</v>
+      </c>
+      <c r="B8" t="n">
+        <v>93345</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Lilla Rullputt, Lilla Rullputt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>517533</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6718997</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>16:43</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>16:43</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135770641</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>135770697</v>
+      </c>
+      <c r="B9" t="n">
+        <v>93345</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Lilla Rullputt, Lilla Rullputt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>517537</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6719013</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135770697</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>135770823</v>
+      </c>
+      <c r="B10" t="n">
+        <v>93345</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Lilla Rullputt, Lilla Rullputt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>517552</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6718984</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>16:49</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>16:49</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Från iår och några fjolårets.</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135770823</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>135771072</v>
+      </c>
+      <c r="B11" t="n">
+        <v>93345</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Lilla Rullputt, Lilla Rullputt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>517548</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6718960</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>16:52</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>16:52</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135771072</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>135771397</v>
+      </c>
+      <c r="B12" t="n">
+        <v>93345</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Lilla Rullputt, Lilla Rullputt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>517547</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6718960</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>16:54</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>16:54</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135771397</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>135771989</v>
+      </c>
+      <c r="B13" t="n">
+        <v>93345</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Lilla Rullputt, Lilla Rullputt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>517528</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6718991</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135771989</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>135772034</v>
+      </c>
+      <c r="B14" t="n">
+        <v>93345</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Lilla Rullputt, Lilla Rullputt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>517502</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6718975</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>17:03</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>17:03</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135772034</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>135772158</v>
+      </c>
+      <c r="B15" t="n">
+        <v>93345</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Lilla Rullputt, Lilla Rullputt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>517469</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6718978</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>17:07</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>17:07</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135772158</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>135772600</v>
+      </c>
+      <c r="B16" t="n">
+        <v>93345</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Lilla Rullputt, Lilla Rullputt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>517571</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6718996</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>17:26</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>17:26</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135772600</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>135772667</v>
+      </c>
+      <c r="B17" t="n">
+        <v>92069</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Lilla Rullputt, Lilla Rullputt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>517573</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6719001</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>17:28</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>17:28</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135772667</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>135769631</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57167</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Lilla Rullputt, Lilla Rullputt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>517358</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6719011</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Under äldre tallar.</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135769631</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>135771364</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57167</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Lilla Rullputt, Lilla Rullputt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>517547</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6718960</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>16:53</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>16:53</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Tappad fjäder.</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135771364</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>135769794</v>
+      </c>
+      <c r="B20" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Lilla Rullputt, Lilla Rullputt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>517389</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6718998</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>16:02</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>16:02</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Bladrosetter spridda över ca 0.5kvdm.</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135769794</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>135769824</v>
+      </c>
+      <c r="B21" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Lilla Rullputt, Lilla Rullputt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>517383</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6719008</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>16:04</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>16:04</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Bladrosetter över knappa 0.5kvdm.</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135769824</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>135769925</v>
+      </c>
+      <c r="B22" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Lilla Rullputt, Lilla Rullputt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>517381</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6719012</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>16:13</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>16:13</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135769925</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>135769965</v>
+      </c>
+      <c r="B23" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Lilla Rullputt, Lilla Rullputt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>517397</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6719007</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135769965</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>135769981</v>
+      </c>
+      <c r="B24" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Lilla Rullputt, Lilla Rullputt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>517403</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6719008</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>16:16</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>16:16</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135769981</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>135769992</v>
+      </c>
+      <c r="B25" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Lilla Rullputt, Lilla Rullputt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>517415</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6719013</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>16:17</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>16:17</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135769992</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>135770396</v>
+      </c>
+      <c r="B26" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Lilla Rullputt, Lilla Rullputt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>517466</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6719012</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>16:33</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>16:33</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135770396</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>135772265</v>
+      </c>
+      <c r="B27" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Lilla Rullputt, Lilla Rullputt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>517459</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6719011</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>17:10</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>17:10</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135772265</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>135773269</v>
+      </c>
+      <c r="B28" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Lilla Rullputt, Lilla Rullputt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>517405</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6719008</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>17:48</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>17:48</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135773269</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>135773307</v>
+      </c>
+      <c r="B29" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Lilla Rullputt, Lilla Rullputt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>517402</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6718995</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>17:49</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>17:49</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135773307</t>
         </is>
       </c>
     </row>
@@ -914,6 +4094,32 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 51953-2025 artfynd.xlsx
+++ b/artfynd/A 51953-2025 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>135772351</v>
       </c>
       <c r="B3" t="n">
-        <v>93337</v>
+        <v>93339</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1039,7 +1039,7 @@
         <v>135770232</v>
       </c>
       <c r="B5" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1160,7 +1160,7 @@
         <v>135770490</v>
       </c>
       <c r="B6" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         <v>135770586</v>
       </c>
       <c r="B7" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
         <v>135770641</v>
       </c>
       <c r="B8" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1514,7 +1514,7 @@
         <v>135770697</v>
       </c>
       <c r="B9" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1635,7 +1635,7 @@
         <v>135770823</v>
       </c>
       <c r="B10" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1761,7 +1761,7 @@
         <v>135771072</v>
       </c>
       <c r="B11" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1882,7 +1882,7 @@
         <v>135771397</v>
       </c>
       <c r="B12" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2003,7 +2003,7 @@
         <v>135771989</v>
       </c>
       <c r="B13" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2124,7 +2124,7 @@
         <v>135772034</v>
       </c>
       <c r="B14" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2245,7 +2245,7 @@
         <v>135772158</v>
       </c>
       <c r="B15" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2357,7 +2357,7 @@
         <v>135772600</v>
       </c>
       <c r="B16" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2478,7 +2478,7 @@
         <v>135772667</v>
       </c>
       <c r="B17" t="n">
-        <v>92069</v>
+        <v>92071</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2838,7 +2838,7 @@
         <v>135769794</v>
       </c>
       <c r="B20" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2969,7 +2969,7 @@
         <v>135769824</v>
       </c>
       <c r="B21" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3100,7 +3100,7 @@
         <v>135769925</v>
       </c>
       <c r="B22" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3226,7 +3226,7 @@
         <v>135769965</v>
       </c>
       <c r="B23" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3352,7 +3352,7 @@
         <v>135769981</v>
       </c>
       <c r="B24" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3478,7 +3478,7 @@
         <v>135769992</v>
       </c>
       <c r="B25" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3604,7 +3604,7 @@
         <v>135770396</v>
       </c>
       <c r="B26" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3735,7 +3735,7 @@
         <v>135772265</v>
       </c>
       <c r="B27" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3852,7 +3852,7 @@
         <v>135773269</v>
       </c>
       <c r="B28" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3969,7 +3969,7 @@
         <v>135773307</v>
       </c>
       <c r="B29" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 51953-2025 artfynd.xlsx
+++ b/artfynd/A 51953-2025 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>135772351</v>
       </c>
       <c r="B3" t="n">
-        <v>93339</v>
+        <v>93354</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1039,7 +1039,7 @@
         <v>135770232</v>
       </c>
       <c r="B5" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1160,7 +1160,7 @@
         <v>135770490</v>
       </c>
       <c r="B6" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         <v>135770586</v>
       </c>
       <c r="B7" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
         <v>135770641</v>
       </c>
       <c r="B8" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1514,7 +1514,7 @@
         <v>135770697</v>
       </c>
       <c r="B9" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1635,7 +1635,7 @@
         <v>135770823</v>
       </c>
       <c r="B10" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1761,7 +1761,7 @@
         <v>135771072</v>
       </c>
       <c r="B11" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1882,7 +1882,7 @@
         <v>135771397</v>
       </c>
       <c r="B12" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2003,7 +2003,7 @@
         <v>135771989</v>
       </c>
       <c r="B13" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2124,7 +2124,7 @@
         <v>135772034</v>
       </c>
       <c r="B14" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2245,7 +2245,7 @@
         <v>135772158</v>
       </c>
       <c r="B15" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2357,7 +2357,7 @@
         <v>135772600</v>
       </c>
       <c r="B16" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2478,7 +2478,7 @@
         <v>135772667</v>
       </c>
       <c r="B17" t="n">
-        <v>92071</v>
+        <v>92085</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
         <v>135769631</v>
       </c>
       <c r="B18" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
         <v>135771364</v>
       </c>
       <c r="B19" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2838,7 +2838,7 @@
         <v>135769794</v>
       </c>
       <c r="B20" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2969,7 +2969,7 @@
         <v>135769824</v>
       </c>
       <c r="B21" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3100,7 +3100,7 @@
         <v>135769925</v>
       </c>
       <c r="B22" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3226,7 +3226,7 @@
         <v>135769965</v>
       </c>
       <c r="B23" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3352,7 +3352,7 @@
         <v>135769981</v>
       </c>
       <c r="B24" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3478,7 +3478,7 @@
         <v>135769992</v>
       </c>
       <c r="B25" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3604,7 +3604,7 @@
         <v>135770396</v>
       </c>
       <c r="B26" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3735,7 +3735,7 @@
         <v>135772265</v>
       </c>
       <c r="B27" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3852,7 +3852,7 @@
         <v>135773269</v>
       </c>
       <c r="B28" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3969,7 +3969,7 @@
         <v>135773307</v>
       </c>
       <c r="B29" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 51953-2025 artfynd.xlsx
+++ b/artfynd/A 51953-2025 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>135772351</v>
       </c>
       <c r="B3" t="n">
-        <v>93354</v>
+        <v>93355</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1039,7 +1039,7 @@
         <v>135770232</v>
       </c>
       <c r="B5" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1160,7 +1160,7 @@
         <v>135770490</v>
       </c>
       <c r="B6" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         <v>135770586</v>
       </c>
       <c r="B7" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
         <v>135770641</v>
       </c>
       <c r="B8" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1514,7 +1514,7 @@
         <v>135770697</v>
       </c>
       <c r="B9" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1635,7 +1635,7 @@
         <v>135770823</v>
       </c>
       <c r="B10" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1761,7 +1761,7 @@
         <v>135771072</v>
       </c>
       <c r="B11" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1882,7 +1882,7 @@
         <v>135771397</v>
       </c>
       <c r="B12" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2003,7 +2003,7 @@
         <v>135771989</v>
       </c>
       <c r="B13" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2124,7 +2124,7 @@
         <v>135772034</v>
       </c>
       <c r="B14" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2245,7 +2245,7 @@
         <v>135772158</v>
       </c>
       <c r="B15" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2357,7 +2357,7 @@
         <v>135772600</v>
       </c>
       <c r="B16" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2478,7 +2478,7 @@
         <v>135772667</v>
       </c>
       <c r="B17" t="n">
-        <v>92085</v>
+        <v>92086</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2838,7 +2838,7 @@
         <v>135769794</v>
       </c>
       <c r="B20" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2969,7 +2969,7 @@
         <v>135769824</v>
       </c>
       <c r="B21" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3100,7 +3100,7 @@
         <v>135769925</v>
       </c>
       <c r="B22" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3226,7 +3226,7 @@
         <v>135769965</v>
       </c>
       <c r="B23" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3352,7 +3352,7 @@
         <v>135769981</v>
       </c>
       <c r="B24" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3478,7 +3478,7 @@
         <v>135769992</v>
       </c>
       <c r="B25" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3604,7 +3604,7 @@
         <v>135770396</v>
       </c>
       <c r="B26" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3735,7 +3735,7 @@
         <v>135772265</v>
       </c>
       <c r="B27" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3852,7 +3852,7 @@
         <v>135773269</v>
       </c>
       <c r="B28" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3969,7 +3969,7 @@
         <v>135773307</v>
       </c>
       <c r="B29" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 51953-2025 artfynd.xlsx
+++ b/artfynd/A 51953-2025 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>135772351</v>
       </c>
       <c r="B3" t="n">
-        <v>93355</v>
+        <v>93356</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1039,7 +1039,7 @@
         <v>135770232</v>
       </c>
       <c r="B5" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1160,7 +1160,7 @@
         <v>135770490</v>
       </c>
       <c r="B6" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         <v>135770586</v>
       </c>
       <c r="B7" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
         <v>135770641</v>
       </c>
       <c r="B8" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1514,7 +1514,7 @@
         <v>135770697</v>
       </c>
       <c r="B9" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1635,7 +1635,7 @@
         <v>135770823</v>
       </c>
       <c r="B10" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1761,7 +1761,7 @@
         <v>135771072</v>
       </c>
       <c r="B11" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1882,7 +1882,7 @@
         <v>135771397</v>
       </c>
       <c r="B12" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2003,7 +2003,7 @@
         <v>135771989</v>
       </c>
       <c r="B13" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2124,7 +2124,7 @@
         <v>135772034</v>
       </c>
       <c r="B14" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2245,7 +2245,7 @@
         <v>135772158</v>
       </c>
       <c r="B15" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2357,7 +2357,7 @@
         <v>135772600</v>
       </c>
       <c r="B16" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2478,7 +2478,7 @@
         <v>135772667</v>
       </c>
       <c r="B17" t="n">
-        <v>92086</v>
+        <v>92087</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2838,7 +2838,7 @@
         <v>135769794</v>
       </c>
       <c r="B20" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2969,7 +2969,7 @@
         <v>135769824</v>
       </c>
       <c r="B21" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3100,7 +3100,7 @@
         <v>135769925</v>
       </c>
       <c r="B22" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3226,7 +3226,7 @@
         <v>135769965</v>
       </c>
       <c r="B23" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3352,7 +3352,7 @@
         <v>135769981</v>
       </c>
       <c r="B24" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3478,7 +3478,7 @@
         <v>135769992</v>
       </c>
       <c r="B25" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3604,7 +3604,7 @@
         <v>135770396</v>
       </c>
       <c r="B26" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3735,7 +3735,7 @@
         <v>135772265</v>
       </c>
       <c r="B27" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3852,7 +3852,7 @@
         <v>135773269</v>
       </c>
       <c r="B28" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3969,7 +3969,7 @@
         <v>135773307</v>
       </c>
       <c r="B29" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 51953-2025 artfynd.xlsx
+++ b/artfynd/A 51953-2025 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>135772351</v>
       </c>
       <c r="B3" t="n">
-        <v>93356</v>
+        <v>93357</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1039,7 +1039,7 @@
         <v>135770232</v>
       </c>
       <c r="B5" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1160,7 +1160,7 @@
         <v>135770490</v>
       </c>
       <c r="B6" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         <v>135770586</v>
       </c>
       <c r="B7" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
         <v>135770641</v>
       </c>
       <c r="B8" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1514,7 +1514,7 @@
         <v>135770697</v>
       </c>
       <c r="B9" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1635,7 +1635,7 @@
         <v>135770823</v>
       </c>
       <c r="B10" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1761,7 +1761,7 @@
         <v>135771072</v>
       </c>
       <c r="B11" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1882,7 +1882,7 @@
         <v>135771397</v>
       </c>
       <c r="B12" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2003,7 +2003,7 @@
         <v>135771989</v>
       </c>
       <c r="B13" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2124,7 +2124,7 @@
         <v>135772034</v>
       </c>
       <c r="B14" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2245,7 +2245,7 @@
         <v>135772158</v>
       </c>
       <c r="B15" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2357,7 +2357,7 @@
         <v>135772600</v>
       </c>
       <c r="B16" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2478,7 +2478,7 @@
         <v>135772667</v>
       </c>
       <c r="B17" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
         <v>135769631</v>
       </c>
       <c r="B18" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
         <v>135771364</v>
       </c>
       <c r="B19" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2838,7 +2838,7 @@
         <v>135769794</v>
       </c>
       <c r="B20" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2969,7 +2969,7 @@
         <v>135769824</v>
       </c>
       <c r="B21" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3100,7 +3100,7 @@
         <v>135769925</v>
       </c>
       <c r="B22" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3226,7 +3226,7 @@
         <v>135769965</v>
       </c>
       <c r="B23" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3352,7 +3352,7 @@
         <v>135769981</v>
       </c>
       <c r="B24" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3478,7 +3478,7 @@
         <v>135769992</v>
       </c>
       <c r="B25" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3604,7 +3604,7 @@
         <v>135770396</v>
       </c>
       <c r="B26" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3735,7 +3735,7 @@
         <v>135772265</v>
       </c>
       <c r="B27" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3852,7 +3852,7 @@
         <v>135773269</v>
       </c>
       <c r="B28" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3969,7 +3969,7 @@
         <v>135773307</v>
       </c>
       <c r="B29" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 51953-2025 artfynd.xlsx
+++ b/artfynd/A 51953-2025 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>135772351</v>
       </c>
       <c r="B3" t="n">
-        <v>93357</v>
+        <v>93363</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1039,7 +1039,7 @@
         <v>135770232</v>
       </c>
       <c r="B5" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1160,7 +1160,7 @@
         <v>135770490</v>
       </c>
       <c r="B6" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         <v>135770586</v>
       </c>
       <c r="B7" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
         <v>135770641</v>
       </c>
       <c r="B8" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1514,7 +1514,7 @@
         <v>135770697</v>
       </c>
       <c r="B9" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1635,7 +1635,7 @@
         <v>135770823</v>
       </c>
       <c r="B10" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1761,7 +1761,7 @@
         <v>135771072</v>
       </c>
       <c r="B11" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1882,7 +1882,7 @@
         <v>135771397</v>
       </c>
       <c r="B12" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2003,7 +2003,7 @@
         <v>135771989</v>
       </c>
       <c r="B13" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2124,7 +2124,7 @@
         <v>135772034</v>
       </c>
       <c r="B14" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2245,7 +2245,7 @@
         <v>135772158</v>
       </c>
       <c r="B15" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2357,7 +2357,7 @@
         <v>135772600</v>
       </c>
       <c r="B16" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2478,7 +2478,7 @@
         <v>135772667</v>
       </c>
       <c r="B17" t="n">
-        <v>92088</v>
+        <v>92094</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
         <v>135769631</v>
       </c>
       <c r="B18" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
         <v>135771364</v>
       </c>
       <c r="B19" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2838,7 +2838,7 @@
         <v>135769794</v>
       </c>
       <c r="B20" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2969,7 +2969,7 @@
         <v>135769824</v>
       </c>
       <c r="B21" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3100,7 +3100,7 @@
         <v>135769925</v>
       </c>
       <c r="B22" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3226,7 +3226,7 @@
         <v>135769965</v>
       </c>
       <c r="B23" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3352,7 +3352,7 @@
         <v>135769981</v>
       </c>
       <c r="B24" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3478,7 +3478,7 @@
         <v>135769992</v>
       </c>
       <c r="B25" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3604,7 +3604,7 @@
         <v>135770396</v>
       </c>
       <c r="B26" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3735,7 +3735,7 @@
         <v>135772265</v>
       </c>
       <c r="B27" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3852,7 +3852,7 @@
         <v>135773269</v>
       </c>
       <c r="B28" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3969,7 +3969,7 @@
         <v>135773307</v>
       </c>
       <c r="B29" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 51953-2025 artfynd.xlsx
+++ b/artfynd/A 51953-2025 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>135772351</v>
       </c>
       <c r="B3" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1039,7 +1039,7 @@
         <v>135770232</v>
       </c>
       <c r="B5" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1160,7 +1160,7 @@
         <v>135770490</v>
       </c>
       <c r="B6" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         <v>135770586</v>
       </c>
       <c r="B7" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
         <v>135770641</v>
       </c>
       <c r="B8" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1514,7 +1514,7 @@
         <v>135770697</v>
       </c>
       <c r="B9" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1635,7 +1635,7 @@
         <v>135770823</v>
       </c>
       <c r="B10" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1761,7 +1761,7 @@
         <v>135771072</v>
       </c>
       <c r="B11" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1882,7 +1882,7 @@
         <v>135771397</v>
       </c>
       <c r="B12" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2003,7 +2003,7 @@
         <v>135771989</v>
       </c>
       <c r="B13" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2124,7 +2124,7 @@
         <v>135772034</v>
       </c>
       <c r="B14" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2245,7 +2245,7 @@
         <v>135772158</v>
       </c>
       <c r="B15" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2357,7 +2357,7 @@
         <v>135772600</v>
       </c>
       <c r="B16" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2478,7 +2478,7 @@
         <v>135772667</v>
       </c>
       <c r="B17" t="n">
-        <v>92094</v>
+        <v>92095</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
         <v>135769631</v>
       </c>
       <c r="B18" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
         <v>135771364</v>
       </c>
       <c r="B19" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2838,7 +2838,7 @@
         <v>135769794</v>
       </c>
       <c r="B20" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2969,7 +2969,7 @@
         <v>135769824</v>
       </c>
       <c r="B21" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3100,7 +3100,7 @@
         <v>135769925</v>
       </c>
       <c r="B22" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3226,7 +3226,7 @@
         <v>135769965</v>
       </c>
       <c r="B23" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3352,7 +3352,7 @@
         <v>135769981</v>
       </c>
       <c r="B24" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3478,7 +3478,7 @@
         <v>135769992</v>
       </c>
       <c r="B25" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3604,7 +3604,7 @@
         <v>135770396</v>
       </c>
       <c r="B26" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3735,7 +3735,7 @@
         <v>135772265</v>
       </c>
       <c r="B27" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3852,7 +3852,7 @@
         <v>135773269</v>
       </c>
       <c r="B28" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3969,7 +3969,7 @@
         <v>135773307</v>
       </c>
       <c r="B29" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 51953-2025 artfynd.xlsx
+++ b/artfynd/A 51953-2025 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>135772351</v>
       </c>
       <c r="B3" t="n">
-        <v>93364</v>
+        <v>93370</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1039,7 +1039,7 @@
         <v>135770232</v>
       </c>
       <c r="B5" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1160,7 +1160,7 @@
         <v>135770490</v>
       </c>
       <c r="B6" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         <v>135770586</v>
       </c>
       <c r="B7" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
         <v>135770641</v>
       </c>
       <c r="B8" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1514,7 +1514,7 @@
         <v>135770697</v>
       </c>
       <c r="B9" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1635,7 +1635,7 @@
         <v>135770823</v>
       </c>
       <c r="B10" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1761,7 +1761,7 @@
         <v>135771072</v>
       </c>
       <c r="B11" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1882,7 +1882,7 @@
         <v>135771397</v>
       </c>
       <c r="B12" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2003,7 +2003,7 @@
         <v>135771989</v>
       </c>
       <c r="B13" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2124,7 +2124,7 @@
         <v>135772034</v>
       </c>
       <c r="B14" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2245,7 +2245,7 @@
         <v>135772158</v>
       </c>
       <c r="B15" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2357,7 +2357,7 @@
         <v>135772600</v>
       </c>
       <c r="B16" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2478,7 +2478,7 @@
         <v>135772667</v>
       </c>
       <c r="B17" t="n">
-        <v>92095</v>
+        <v>92101</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2838,7 +2838,7 @@
         <v>135769794</v>
       </c>
       <c r="B20" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2969,7 +2969,7 @@
         <v>135769824</v>
       </c>
       <c r="B21" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3100,7 +3100,7 @@
         <v>135769925</v>
       </c>
       <c r="B22" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3226,7 +3226,7 @@
         <v>135769965</v>
       </c>
       <c r="B23" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3352,7 +3352,7 @@
         <v>135769981</v>
       </c>
       <c r="B24" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3478,7 +3478,7 @@
         <v>135769992</v>
       </c>
       <c r="B25" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3604,7 +3604,7 @@
         <v>135770396</v>
       </c>
       <c r="B26" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3735,7 +3735,7 @@
         <v>135772265</v>
       </c>
       <c r="B27" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3852,7 +3852,7 @@
         <v>135773269</v>
       </c>
       <c r="B28" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3969,7 +3969,7 @@
         <v>135773307</v>
       </c>
       <c r="B29" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 51953-2025 artfynd.xlsx
+++ b/artfynd/A 51953-2025 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>135772351</v>
       </c>
       <c r="B3" t="n">
-        <v>93370</v>
+        <v>93377</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1039,7 +1039,7 @@
         <v>135770232</v>
       </c>
       <c r="B5" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1160,7 +1160,7 @@
         <v>135770490</v>
       </c>
       <c r="B6" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         <v>135770586</v>
       </c>
       <c r="B7" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
         <v>135770641</v>
       </c>
       <c r="B8" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1514,7 +1514,7 @@
         <v>135770697</v>
       </c>
       <c r="B9" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1635,7 +1635,7 @@
         <v>135770823</v>
       </c>
       <c r="B10" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1761,7 +1761,7 @@
         <v>135771072</v>
       </c>
       <c r="B11" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1882,7 +1882,7 @@
         <v>135771397</v>
       </c>
       <c r="B12" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2003,7 +2003,7 @@
         <v>135771989</v>
       </c>
       <c r="B13" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2124,7 +2124,7 @@
         <v>135772034</v>
       </c>
       <c r="B14" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2245,7 +2245,7 @@
         <v>135772158</v>
       </c>
       <c r="B15" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2357,7 +2357,7 @@
         <v>135772600</v>
       </c>
       <c r="B16" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2478,7 +2478,7 @@
         <v>135772667</v>
       </c>
       <c r="B17" t="n">
-        <v>92101</v>
+        <v>92108</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
         <v>135769631</v>
       </c>
       <c r="B18" t="n">
-        <v>57175</v>
+        <v>57180</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
         <v>135771364</v>
       </c>
       <c r="B19" t="n">
-        <v>57175</v>
+        <v>57180</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2838,7 +2838,7 @@
         <v>135769794</v>
       </c>
       <c r="B20" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2969,7 +2969,7 @@
         <v>135769824</v>
       </c>
       <c r="B21" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3100,7 +3100,7 @@
         <v>135769925</v>
       </c>
       <c r="B22" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3226,7 +3226,7 @@
         <v>135769965</v>
       </c>
       <c r="B23" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3352,7 +3352,7 @@
         <v>135769981</v>
       </c>
       <c r="B24" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3478,7 +3478,7 @@
         <v>135769992</v>
       </c>
       <c r="B25" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3604,7 +3604,7 @@
         <v>135770396</v>
       </c>
       <c r="B26" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3735,7 +3735,7 @@
         <v>135772265</v>
       </c>
       <c r="B27" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3852,7 +3852,7 @@
         <v>135773269</v>
       </c>
       <c r="B28" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3969,7 +3969,7 @@
         <v>135773307</v>
       </c>
       <c r="B29" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
